--- a/CareerOneStop_Data.xlsx
+++ b/CareerOneStop_Data.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cjconti/Documents/Web Design/career-one-stop-vs-nj-expenses/public/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAD3EB1-F353-9E4B-8F7A-2ED0FDB8AD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="660" windowWidth="25780" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1543,8 +1549,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1607,13 +1613,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1651,7 +1665,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1685,6 +1699,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1719,9 +1734,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1894,11 +1910,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P481"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1948,7 +1964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -1968,7 +1984,7 @@
         <v>663</v>
       </c>
       <c r="G2">
-        <v>19.01</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="H2">
         <v>39500</v>
@@ -1998,7 +2014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -2018,7 +2034,7 @@
         <v>694</v>
       </c>
       <c r="G3">
-        <v>17.83</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="H3">
         <v>37100</v>
@@ -2048,7 +2064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5</v>
       </c>
@@ -2098,7 +2114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>7</v>
       </c>
@@ -2148,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>8</v>
       </c>
@@ -2198,7 +2214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>9</v>
       </c>
@@ -2218,7 +2234,7 @@
         <v>730</v>
       </c>
       <c r="G7">
-        <v>16.42</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="H7">
         <v>34200</v>
@@ -2248,7 +2264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>13</v>
       </c>
@@ -2268,7 +2284,7 @@
         <v>27</v>
       </c>
       <c r="G8">
-        <v>83.51000000000001</v>
+        <v>83.51</v>
       </c>
       <c r="H8">
         <v>173700</v>
@@ -2298,7 +2314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>16</v>
       </c>
@@ -2348,7 +2364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>17</v>
       </c>
@@ -2398,7 +2414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>20</v>
       </c>
@@ -2448,7 +2464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>22</v>
       </c>
@@ -2468,7 +2484,7 @@
         <v>38</v>
       </c>
       <c r="G12">
-        <v>77.65000000000001</v>
+        <v>77.650000000000006</v>
       </c>
       <c r="H12">
         <v>161500</v>
@@ -2498,7 +2514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>23</v>
       </c>
@@ -2548,7 +2564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>24</v>
       </c>
@@ -2598,7 +2614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>27</v>
       </c>
@@ -2648,7 +2664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>28</v>
       </c>
@@ -2698,7 +2714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>31</v>
       </c>
@@ -2748,7 +2764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>32</v>
       </c>
@@ -2798,7 +2814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>33</v>
       </c>
@@ -2848,7 +2864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>34</v>
       </c>
@@ -2889,7 +2905,7 @@
         <v>1563400</v>
       </c>
       <c r="N20">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O20" t="s">
         <v>495</v>
@@ -2898,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:16">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>35</v>
       </c>
@@ -2948,7 +2964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>36</v>
       </c>
@@ -2989,7 +3005,7 @@
         <v>1158600</v>
       </c>
       <c r="N22">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O22" t="s">
         <v>495</v>
@@ -2998,7 +3014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>38</v>
       </c>
@@ -3048,7 +3064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>40</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>674</v>
       </c>
       <c r="G24">
-        <v>18.49</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="H24">
         <v>38500</v>
@@ -3098,7 +3114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>41</v>
       </c>
@@ -3139,7 +3155,7 @@
         <v>1004700</v>
       </c>
       <c r="N25">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O25" t="s">
         <v>497</v>
@@ -3148,7 +3164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>42</v>
       </c>
@@ -3198,7 +3214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>43</v>
       </c>
@@ -3248,7 +3264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>44</v>
       </c>
@@ -3268,7 +3284,7 @@
         <v>18</v>
       </c>
       <c r="G28">
-        <v>97.81999999999999</v>
+        <v>97.82</v>
       </c>
       <c r="H28">
         <v>203500</v>
@@ -3298,7 +3314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>45</v>
       </c>
@@ -3348,7 +3364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>47</v>
       </c>
@@ -3398,7 +3414,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>50</v>
       </c>
@@ -3448,7 +3464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>52</v>
       </c>
@@ -3498,7 +3514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>53</v>
       </c>
@@ -3548,7 +3564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>55</v>
       </c>
@@ -3568,7 +3584,7 @@
         <v>261</v>
       </c>
       <c r="G34">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H34">
         <v>80700</v>
@@ -3598,7 +3614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>56</v>
       </c>
@@ -3648,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>57</v>
       </c>
@@ -3698,7 +3714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>60</v>
       </c>
@@ -3748,7 +3764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>61</v>
       </c>
@@ -3798,7 +3814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>62</v>
       </c>
@@ -3848,7 +3864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>63</v>
       </c>
@@ -3868,7 +3884,7 @@
         <v>57</v>
       </c>
       <c r="G40">
-        <v>66.45999999999999</v>
+        <v>66.459999999999994</v>
       </c>
       <c r="H40">
         <v>138200</v>
@@ -3898,7 +3914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>64</v>
       </c>
@@ -3918,7 +3934,7 @@
         <v>28</v>
       </c>
       <c r="G41">
-        <v>83.18000000000001</v>
+        <v>83.18</v>
       </c>
       <c r="H41">
         <v>173000</v>
@@ -3948,7 +3964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>65</v>
       </c>
@@ -3968,7 +3984,7 @@
         <v>321</v>
       </c>
       <c r="G42">
-        <v>36.13</v>
+        <v>36.130000000000003</v>
       </c>
       <c r="H42">
         <v>75200</v>
@@ -3998,7 +4014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>67</v>
       </c>
@@ -4048,7 +4064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>68</v>
       </c>
@@ -4068,7 +4084,7 @@
         <v>246</v>
       </c>
       <c r="G44">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="H44">
         <v>82400</v>
@@ -4098,7 +4114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>69</v>
       </c>
@@ -4148,7 +4164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>70</v>
       </c>
@@ -4168,7 +4184,7 @@
         <v>705</v>
       </c>
       <c r="G46">
-        <v>17.49</v>
+        <v>17.489999999999998</v>
       </c>
       <c r="H46">
         <v>36400</v>
@@ -4189,7 +4205,7 @@
         <v>224800</v>
       </c>
       <c r="N46">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O46" t="s">
         <v>496</v>
@@ -4198,7 +4214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>71</v>
       </c>
@@ -4248,7 +4264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>72</v>
       </c>
@@ -4298,7 +4314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>73</v>
       </c>
@@ -4348,7 +4364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>74</v>
       </c>
@@ -4398,7 +4414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>75</v>
       </c>
@@ -4448,7 +4464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>77</v>
       </c>
@@ -4498,7 +4514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>78</v>
       </c>
@@ -4539,7 +4555,7 @@
         <v>433700</v>
       </c>
       <c r="N53">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O53" t="s">
         <v>497</v>
@@ -4548,7 +4564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>79</v>
       </c>
@@ -4598,7 +4614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>80</v>
       </c>
@@ -4648,7 +4664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>81</v>
       </c>
@@ -4698,7 +4714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>82</v>
       </c>
@@ -4748,7 +4764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>85</v>
       </c>
@@ -4768,7 +4784,7 @@
         <v>650</v>
       </c>
       <c r="G58">
-        <v>19.65</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="H58">
         <v>40900</v>
@@ -4798,7 +4814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>87</v>
       </c>
@@ -4848,7 +4864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>88</v>
       </c>
@@ -4898,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>89</v>
       </c>
@@ -4948,7 +4964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>90</v>
       </c>
@@ -4968,7 +4984,7 @@
         <v>11</v>
       </c>
       <c r="G62">
-        <v>137.02</v>
+        <v>137.02000000000001</v>
       </c>
       <c r="H62">
         <v>285000</v>
@@ -4998,7 +5014,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>92</v>
       </c>
@@ -5048,7 +5064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>92</v>
       </c>
@@ -5098,7 +5114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>95</v>
       </c>
@@ -5148,7 +5164,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>97</v>
       </c>
@@ -5198,7 +5214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>98</v>
       </c>
@@ -5248,7 +5264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>100</v>
       </c>
@@ -5298,7 +5314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>102</v>
       </c>
@@ -5348,7 +5364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>105</v>
       </c>
@@ -5368,7 +5384,7 @@
         <v>46</v>
       </c>
       <c r="G70">
-        <v>76.23999999999999</v>
+        <v>76.239999999999995</v>
       </c>
       <c r="H70">
         <v>158600</v>
@@ -5398,7 +5414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>107</v>
       </c>
@@ -5448,7 +5464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>109</v>
       </c>
@@ -5498,7 +5514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>110</v>
       </c>
@@ -5548,7 +5564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>112</v>
       </c>
@@ -5598,7 +5614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>112</v>
       </c>
@@ -5648,7 +5664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>114</v>
       </c>
@@ -5668,7 +5684,7 @@
         <v>694</v>
       </c>
       <c r="G76">
-        <v>17.83</v>
+        <v>17.829999999999998</v>
       </c>
       <c r="H76">
         <v>37100</v>
@@ -5698,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>115</v>
       </c>
@@ -5718,7 +5734,7 @@
         <v>717</v>
       </c>
       <c r="G77">
-        <v>17.24</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="H77">
         <v>35900</v>
@@ -5748,7 +5764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>116</v>
       </c>
@@ -5798,7 +5814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>117</v>
       </c>
@@ -5848,7 +5864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>118</v>
       </c>
@@ -5898,7 +5914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>119</v>
       </c>
@@ -5939,7 +5955,7 @@
         <v>260300</v>
       </c>
       <c r="N81">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O81" t="s">
         <v>496</v>
@@ -5948,7 +5964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>120</v>
       </c>
@@ -5998,7 +6014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>121</v>
       </c>
@@ -6048,7 +6064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>123</v>
       </c>
@@ -6068,7 +6084,7 @@
         <v>369</v>
       </c>
       <c r="G84">
-        <v>32.91</v>
+        <v>32.909999999999997</v>
       </c>
       <c r="H84">
         <v>68500</v>
@@ -6098,7 +6114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>124</v>
       </c>
@@ -6148,7 +6164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>126</v>
       </c>
@@ -6198,7 +6214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>127</v>
       </c>
@@ -6248,7 +6264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>128</v>
       </c>
@@ -6298,7 +6314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>129</v>
       </c>
@@ -6348,7 +6364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>130</v>
       </c>
@@ -6368,7 +6384,7 @@
         <v>16</v>
       </c>
       <c r="G90">
-        <v>99.54000000000001</v>
+        <v>99.54</v>
       </c>
       <c r="H90">
         <v>207000</v>
@@ -6398,7 +6414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>131</v>
       </c>
@@ -6448,7 +6464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>132</v>
       </c>
@@ -6498,7 +6514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>132</v>
       </c>
@@ -6548,7 +6564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>135</v>
       </c>
@@ -6598,7 +6614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>136</v>
       </c>
@@ -6648,7 +6664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>137</v>
       </c>
@@ -6668,7 +6684,7 @@
         <v>336</v>
       </c>
       <c r="G96">
-        <v>35.48</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="H96">
         <v>73800</v>
@@ -6698,7 +6714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>140</v>
       </c>
@@ -6748,7 +6764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>141</v>
       </c>
@@ -6789,7 +6805,7 @@
         <v>211300</v>
       </c>
       <c r="N98">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O98" t="s">
         <v>498</v>
@@ -6798,7 +6814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>141</v>
       </c>
@@ -6848,7 +6864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>143</v>
       </c>
@@ -6898,7 +6914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>146</v>
       </c>
@@ -6948,7 +6964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>147</v>
       </c>
@@ -6998,7 +7014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>147</v>
       </c>
@@ -7048,7 +7064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>149</v>
       </c>
@@ -7098,7 +7114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>150</v>
       </c>
@@ -7148,7 +7164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>151</v>
       </c>
@@ -7168,7 +7184,7 @@
         <v>266</v>
       </c>
       <c r="G106">
-        <v>38.52</v>
+        <v>38.520000000000003</v>
       </c>
       <c r="H106">
         <v>80100</v>
@@ -7198,7 +7214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>152</v>
       </c>
@@ -7248,7 +7264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>153</v>
       </c>
@@ -7289,7 +7305,7 @@
         <v>159100</v>
       </c>
       <c r="N108">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O108" t="s">
         <v>495</v>
@@ -7298,7 +7314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>154</v>
       </c>
@@ -7318,7 +7334,7 @@
         <v>233</v>
       </c>
       <c r="G109">
-        <v>40.45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="H109">
         <v>84100</v>
@@ -7348,7 +7364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>157</v>
       </c>
@@ -7398,7 +7414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>158</v>
       </c>
@@ -7448,7 +7464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>160</v>
       </c>
@@ -7498,7 +7514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>161</v>
       </c>
@@ -7539,7 +7555,7 @@
         <v>237200</v>
       </c>
       <c r="N113">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O113" t="s">
         <v>497</v>
@@ -7548,7 +7564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>162</v>
       </c>
@@ -7598,7 +7614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>163</v>
       </c>
@@ -7648,7 +7664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>165</v>
       </c>
@@ -7668,7 +7684,7 @@
         <v>23</v>
       </c>
       <c r="G116">
-        <v>86.84999999999999</v>
+        <v>86.85</v>
       </c>
       <c r="H116">
         <v>180600</v>
@@ -7698,7 +7714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>165</v>
       </c>
@@ -7748,7 +7764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>168</v>
       </c>
@@ -7798,7 +7814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>169</v>
       </c>
@@ -7848,7 +7864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>170</v>
       </c>
@@ -7895,7 +7911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>171</v>
       </c>
@@ -7945,7 +7961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>172</v>
       </c>
@@ -7995,7 +8011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>173</v>
       </c>
@@ -8045,7 +8061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>174</v>
       </c>
@@ -8095,7 +8111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>175</v>
       </c>
@@ -8145,7 +8161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>176</v>
       </c>
@@ -8195,7 +8211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>176</v>
       </c>
@@ -8245,7 +8261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>179</v>
       </c>
@@ -8265,7 +8281,7 @@
         <v>65</v>
       </c>
       <c r="G128">
-        <v>64.81999999999999</v>
+        <v>64.819999999999993</v>
       </c>
       <c r="H128">
         <v>134800</v>
@@ -8286,7 +8302,7 @@
         <v>234900</v>
       </c>
       <c r="N128">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O128" t="s">
         <v>497</v>
@@ -8295,7 +8311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>180</v>
       </c>
@@ -8345,7 +8361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>181</v>
       </c>
@@ -8395,7 +8411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>181</v>
       </c>
@@ -8445,7 +8461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>183</v>
       </c>
@@ -8495,7 +8511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>183</v>
       </c>
@@ -8545,7 +8561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>188</v>
       </c>
@@ -8595,7 +8611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>189</v>
       </c>
@@ -8645,7 +8661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>190</v>
       </c>
@@ -8695,7 +8711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>191</v>
       </c>
@@ -8745,7 +8761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>192</v>
       </c>
@@ -8795,7 +8811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>193</v>
       </c>
@@ -8845,7 +8861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>195</v>
       </c>
@@ -8895,7 +8911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>196</v>
       </c>
@@ -8936,7 +8952,7 @@
         <v>205700</v>
       </c>
       <c r="N141">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O141" t="s">
         <v>497</v>
@@ -8945,7 +8961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>196</v>
       </c>
@@ -8995,7 +9011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>198</v>
       </c>
@@ -9015,7 +9031,7 @@
         <v>713</v>
       </c>
       <c r="G143">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="H143">
         <v>36100</v>
@@ -9045,7 +9061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>200</v>
       </c>
@@ -9095,7 +9111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>201</v>
       </c>
@@ -9145,7 +9161,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>202</v>
       </c>
@@ -9195,7 +9211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>203</v>
       </c>
@@ -9245,7 +9261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>204</v>
       </c>
@@ -9265,7 +9281,7 @@
         <v>29</v>
       </c>
       <c r="G148">
-        <v>82.90000000000001</v>
+        <v>82.9</v>
       </c>
       <c r="H148">
         <v>172400</v>
@@ -9295,7 +9311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>205</v>
       </c>
@@ -9345,7 +9361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>205</v>
       </c>
@@ -9395,7 +9411,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>207</v>
       </c>
@@ -9445,7 +9461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>209</v>
       </c>
@@ -9495,7 +9511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>210</v>
       </c>
@@ -9545,7 +9561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>210</v>
       </c>
@@ -9565,7 +9581,7 @@
         <v>347</v>
       </c>
       <c r="G154">
-        <v>34.59</v>
+        <v>34.590000000000003</v>
       </c>
       <c r="H154">
         <v>71900</v>
@@ -9595,7 +9611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>212</v>
       </c>
@@ -9636,7 +9652,7 @@
         <v>182100</v>
       </c>
       <c r="N155">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="O155" t="s">
         <v>497</v>
@@ -9645,7 +9661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>213</v>
       </c>
@@ -9695,7 +9711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>214</v>
       </c>
@@ -9745,7 +9761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>215</v>
       </c>
@@ -9795,7 +9811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>216</v>
       </c>
@@ -9815,7 +9831,7 @@
         <v>251</v>
       </c>
       <c r="G159">
-        <v>39.27</v>
+        <v>39.270000000000003</v>
       </c>
       <c r="H159">
         <v>81700</v>
@@ -9845,7 +9861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>217</v>
       </c>
@@ -9865,7 +9881,7 @@
         <v>668</v>
       </c>
       <c r="G160">
-        <v>18.85</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="H160">
         <v>39200</v>
@@ -9895,7 +9911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>219</v>
       </c>
@@ -9915,7 +9931,7 @@
         <v>252</v>
       </c>
       <c r="G161">
-        <v>39.23</v>
+        <v>39.229999999999997</v>
       </c>
       <c r="H161">
         <v>81600</v>
@@ -9945,7 +9961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>221</v>
       </c>
@@ -9995,7 +10011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>222</v>
       </c>
@@ -10045,7 +10061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>223</v>
       </c>
@@ -10095,7 +10111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>225</v>
       </c>
@@ -10145,7 +10161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>227</v>
       </c>
@@ -10195,7 +10211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>229</v>
       </c>
@@ -10236,7 +10252,7 @@
         <v>185400</v>
       </c>
       <c r="N167">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O167" t="s">
         <v>495</v>
@@ -10245,7 +10261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>230</v>
       </c>
@@ -10295,7 +10311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>233</v>
       </c>
@@ -10345,7 +10361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>234</v>
       </c>
@@ -10395,7 +10411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>236</v>
       </c>
@@ -10445,7 +10461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>239</v>
       </c>
@@ -10495,7 +10511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>240</v>
       </c>
@@ -10545,7 +10561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>243</v>
       </c>
@@ -10595,7 +10611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>244</v>
       </c>
@@ -10645,7 +10661,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>245</v>
       </c>
@@ -10695,7 +10711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>247</v>
       </c>
@@ -10745,7 +10761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>247</v>
       </c>
@@ -10795,7 +10811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>249</v>
       </c>
@@ -10845,7 +10861,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>251</v>
       </c>
@@ -10895,7 +10911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>253</v>
       </c>
@@ -10942,7 +10958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>254</v>
       </c>
@@ -10989,7 +11005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>255</v>
       </c>
@@ -11039,7 +11055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>256</v>
       </c>
@@ -11059,7 +11075,7 @@
         <v>63</v>
       </c>
       <c r="G184">
-        <v>65.04000000000001</v>
+        <v>65.040000000000006</v>
       </c>
       <c r="H184">
         <v>135300</v>
@@ -11089,7 +11105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>257</v>
       </c>
@@ -11136,7 +11152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>257</v>
       </c>
@@ -11186,7 +11202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>260</v>
       </c>
@@ -11236,7 +11252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>261</v>
       </c>
@@ -11286,7 +11302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>262</v>
       </c>
@@ -11336,7 +11352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>263</v>
       </c>
@@ -11386,7 +11402,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>264</v>
       </c>
@@ -11436,7 +11452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>265</v>
       </c>
@@ -11486,7 +11502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>269</v>
       </c>
@@ -11536,7 +11552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>270</v>
       </c>
@@ -11586,7 +11602,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>271</v>
       </c>
@@ -11606,7 +11622,7 @@
         <v>301</v>
       </c>
       <c r="G195">
-        <v>37.12</v>
+        <v>37.119999999999997</v>
       </c>
       <c r="H195">
         <v>77200</v>
@@ -11636,7 +11652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>272</v>
       </c>
@@ -11686,7 +11702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>273</v>
       </c>
@@ -11736,7 +11752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>273</v>
       </c>
@@ -11786,7 +11802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>275</v>
       </c>
@@ -11836,7 +11852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>275</v>
       </c>
@@ -11886,7 +11902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>275</v>
       </c>
@@ -11936,7 +11952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>281</v>
       </c>
@@ -11956,7 +11972,7 @@
         <v>26</v>
       </c>
       <c r="G202">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="H202">
         <v>174500</v>
@@ -11986,7 +12002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>282</v>
       </c>
@@ -12027,7 +12043,7 @@
         <v>137900</v>
       </c>
       <c r="N203">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O203" t="s">
         <v>497</v>
@@ -12036,7 +12052,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>283</v>
       </c>
@@ -12086,7 +12102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>283</v>
       </c>
@@ -12136,7 +12152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>286</v>
       </c>
@@ -12183,7 +12199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>288</v>
       </c>
@@ -12203,7 +12219,7 @@
         <v>369</v>
       </c>
       <c r="G207">
-        <v>32.91</v>
+        <v>32.909999999999997</v>
       </c>
       <c r="H207">
         <v>68500</v>
@@ -12233,7 +12249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>288</v>
       </c>
@@ -12283,7 +12299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>291</v>
       </c>
@@ -12303,7 +12319,7 @@
         <v>286</v>
       </c>
       <c r="G209">
-        <v>37.59</v>
+        <v>37.590000000000003</v>
       </c>
       <c r="H209">
         <v>78200</v>
@@ -12333,7 +12349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>292</v>
       </c>
@@ -12383,7 +12399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>292</v>
       </c>
@@ -12403,7 +12419,7 @@
         <v>335</v>
       </c>
       <c r="G211">
-        <v>35.59</v>
+        <v>35.590000000000003</v>
       </c>
       <c r="H211">
         <v>74000</v>
@@ -12433,7 +12449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>297</v>
       </c>
@@ -12483,7 +12499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>297</v>
       </c>
@@ -12533,7 +12549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>299</v>
       </c>
@@ -12553,7 +12569,7 @@
         <v>42</v>
       </c>
       <c r="G214">
-        <v>76.98999999999999</v>
+        <v>76.989999999999995</v>
       </c>
       <c r="H214">
         <v>160100</v>
@@ -12583,7 +12599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>300</v>
       </c>
@@ -12633,7 +12649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>301</v>
       </c>
@@ -12683,7 +12699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>303</v>
       </c>
@@ -12733,7 +12749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>305</v>
       </c>
@@ -12783,7 +12799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>306</v>
       </c>
@@ -12833,7 +12849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>307</v>
       </c>
@@ -12883,7 +12899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>308</v>
       </c>
@@ -12924,7 +12940,7 @@
         <v>64400</v>
       </c>
       <c r="N221">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O221" t="s">
         <v>497</v>
@@ -12933,7 +12949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>310</v>
       </c>
@@ -12983,7 +12999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>311</v>
       </c>
@@ -13033,7 +13049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>314</v>
       </c>
@@ -13074,7 +13090,7 @@
         <v>103900</v>
       </c>
       <c r="N224">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O224" t="s">
         <v>495</v>
@@ -13083,7 +13099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>316</v>
       </c>
@@ -13133,7 +13149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>317</v>
       </c>
@@ -13171,7 +13187,7 @@
         <v>70800</v>
       </c>
       <c r="N226">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O226" t="s">
         <v>497</v>
@@ -13180,7 +13196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>317</v>
       </c>
@@ -13230,7 +13246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>317</v>
       </c>
@@ -13280,7 +13296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>323</v>
       </c>
@@ -13327,7 +13343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>325</v>
       </c>
@@ -13374,7 +13390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>326</v>
       </c>
@@ -13394,7 +13410,7 @@
         <v>343</v>
       </c>
       <c r="G231">
-        <v>34.84</v>
+        <v>34.840000000000003</v>
       </c>
       <c r="H231">
         <v>72500</v>
@@ -13424,7 +13440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>327</v>
       </c>
@@ -13474,7 +13490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>330</v>
       </c>
@@ -13524,7 +13540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>331</v>
       </c>
@@ -13544,7 +13560,7 @@
         <v>339</v>
       </c>
       <c r="G234">
-        <v>35.27</v>
+        <v>35.270000000000003</v>
       </c>
       <c r="H234">
         <v>73400</v>
@@ -13574,7 +13590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>332</v>
       </c>
@@ -13624,7 +13640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>333</v>
       </c>
@@ -13674,7 +13690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>333</v>
       </c>
@@ -13721,7 +13737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>335</v>
       </c>
@@ -13741,7 +13757,7 @@
         <v>354</v>
       </c>
       <c r="G238">
-        <v>34.16</v>
+        <v>34.159999999999997</v>
       </c>
       <c r="H238">
         <v>71000</v>
@@ -13771,7 +13787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>338</v>
       </c>
@@ -13821,7 +13837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>339</v>
       </c>
@@ -13871,7 +13887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>339</v>
       </c>
@@ -13921,7 +13937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>343</v>
       </c>
@@ -13968,7 +13984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>345</v>
       </c>
@@ -13988,7 +14004,7 @@
         <v>378</v>
       </c>
       <c r="G243">
-        <v>32.02</v>
+        <v>32.020000000000003</v>
       </c>
       <c r="H243">
         <v>66600</v>
@@ -14018,7 +14034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>346</v>
       </c>
@@ -14068,7 +14084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>347</v>
       </c>
@@ -14118,7 +14134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>347</v>
       </c>
@@ -14168,7 +14184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>347</v>
       </c>
@@ -14218,7 +14234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>350</v>
       </c>
@@ -14238,7 +14254,7 @@
         <v>54</v>
       </c>
       <c r="G248">
-        <v>67.70999999999999</v>
+        <v>67.709999999999994</v>
       </c>
       <c r="H248">
         <v>140800</v>
@@ -14268,7 +14284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>351</v>
       </c>
@@ -14318,7 +14334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>351</v>
       </c>
@@ -14368,7 +14384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>351</v>
       </c>
@@ -14418,7 +14434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>354</v>
       </c>
@@ -14468,7 +14484,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>357</v>
       </c>
@@ -14518,7 +14534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>358</v>
       </c>
@@ -14559,7 +14575,7 @@
         <v>208600</v>
       </c>
       <c r="N254">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O254" t="s">
         <v>498</v>
@@ -14568,7 +14584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>359</v>
       </c>
@@ -14618,7 +14634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>360</v>
       </c>
@@ -14668,7 +14684,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:16">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>361</v>
       </c>
@@ -14718,7 +14734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="258" spans="1:16">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>362</v>
       </c>
@@ -14768,7 +14784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:16">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>363</v>
       </c>
@@ -14809,7 +14825,7 @@
         <v>82400</v>
       </c>
       <c r="N259">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O259" t="s">
         <v>497</v>
@@ -14818,7 +14834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:16">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>363</v>
       </c>
@@ -14868,7 +14884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:16">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>366</v>
       </c>
@@ -14918,7 +14934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:16">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>367</v>
       </c>
@@ -14965,7 +14981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="263" spans="1:16">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>367</v>
       </c>
@@ -15015,7 +15031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:16">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>369</v>
       </c>
@@ -15062,7 +15078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:16">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>369</v>
       </c>
@@ -15112,7 +15128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:16">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>371</v>
       </c>
@@ -15162,7 +15178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:16">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>375</v>
       </c>
@@ -15212,7 +15228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:16">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>375</v>
       </c>
@@ -15262,7 +15278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:16">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>377</v>
       </c>
@@ -15312,7 +15328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:16">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>380</v>
       </c>
@@ -15332,7 +15348,7 @@
         <v>40</v>
       </c>
       <c r="G270">
-        <v>77.18000000000001</v>
+        <v>77.180000000000007</v>
       </c>
       <c r="H270">
         <v>160500</v>
@@ -15362,7 +15378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:16">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>381</v>
       </c>
@@ -15382,7 +15398,7 @@
         <v>53</v>
       </c>
       <c r="G271">
-        <v>68.65000000000001</v>
+        <v>68.650000000000006</v>
       </c>
       <c r="H271">
         <v>142800</v>
@@ -15412,7 +15428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:16">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>381</v>
       </c>
@@ -15462,7 +15478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:16">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>383</v>
       </c>
@@ -15512,7 +15528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:16">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>386</v>
       </c>
@@ -15562,7 +15578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:16">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>386</v>
       </c>
@@ -15612,7 +15628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:16">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>388</v>
       </c>
@@ -15662,7 +15678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:16">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>389</v>
       </c>
@@ -15682,7 +15698,7 @@
         <v>322</v>
       </c>
       <c r="G277">
-        <v>36.09</v>
+        <v>36.090000000000003</v>
       </c>
       <c r="H277">
         <v>75100</v>
@@ -15712,7 +15728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:16">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>389</v>
       </c>
@@ -15762,7 +15778,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:16">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>391</v>
       </c>
@@ -15812,7 +15828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:16">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>392</v>
       </c>
@@ -15862,7 +15878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:16">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>394</v>
       </c>
@@ -15912,7 +15928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:16">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>396</v>
       </c>
@@ -15962,7 +15978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:16">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>396</v>
       </c>
@@ -16012,7 +16028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:16">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>398</v>
       </c>
@@ -16062,7 +16078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:16">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>399</v>
       </c>
@@ -16112,7 +16128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:16">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>401</v>
       </c>
@@ -16162,7 +16178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:16">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>401</v>
       </c>
@@ -16212,7 +16228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:16">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>404</v>
       </c>
@@ -16253,7 +16269,7 @@
         <v>135800</v>
       </c>
       <c r="N288">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O288" t="s">
         <v>497</v>
@@ -16262,7 +16278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:16">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>404</v>
       </c>
@@ -16312,7 +16328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:16">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>406</v>
       </c>
@@ -16359,7 +16375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:16">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>408</v>
       </c>
@@ -16409,7 +16425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:16">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>409</v>
       </c>
@@ -16459,7 +16475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:16">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>409</v>
       </c>
@@ -16509,7 +16525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:16">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>411</v>
       </c>
@@ -16559,7 +16575,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:16">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>411</v>
       </c>
@@ -16609,7 +16625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:16">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>413</v>
       </c>
@@ -16650,7 +16666,7 @@
         <v>47200</v>
       </c>
       <c r="N296">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O296" t="s">
         <v>497</v>
@@ -16659,7 +16675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:16">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>414</v>
       </c>
@@ -16700,7 +16716,7 @@
         <v>16200</v>
       </c>
       <c r="N297">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O297" t="s">
         <v>497</v>
@@ -16709,7 +16725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:16">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>416</v>
       </c>
@@ -16759,7 +16775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:16">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>419</v>
       </c>
@@ -16800,7 +16816,7 @@
         <v>16400</v>
       </c>
       <c r="N299">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O299" t="s">
         <v>498</v>
@@ -16809,7 +16825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:16">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>419</v>
       </c>
@@ -16859,7 +16875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:16">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>421</v>
       </c>
@@ -16879,7 +16895,7 @@
         <v>17</v>
       </c>
       <c r="G301">
-        <v>98.15000000000001</v>
+        <v>98.15</v>
       </c>
       <c r="H301">
         <v>204200</v>
@@ -16909,7 +16925,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:16">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>422</v>
       </c>
@@ -16959,7 +16975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:16">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>424</v>
       </c>
@@ -17009,7 +17025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:16">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>425</v>
       </c>
@@ -17059,7 +17075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>425</v>
       </c>
@@ -17109,7 +17125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>428</v>
       </c>
@@ -17159,7 +17175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>430</v>
       </c>
@@ -17179,7 +17195,7 @@
         <v>66</v>
       </c>
       <c r="G307">
-        <v>64.04000000000001</v>
+        <v>64.040000000000006</v>
       </c>
       <c r="H307">
         <v>133200</v>
@@ -17209,7 +17225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>433</v>
       </c>
@@ -17229,7 +17245,7 @@
         <v>64</v>
       </c>
       <c r="G308">
-        <v>64.90000000000001</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="H308">
         <v>135000</v>
@@ -17259,7 +17275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>433</v>
       </c>
@@ -17309,7 +17325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>433</v>
       </c>
@@ -17359,7 +17375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>433</v>
       </c>
@@ -17409,7 +17425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>438</v>
       </c>
@@ -17459,7 +17475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>438</v>
       </c>
@@ -17509,7 +17525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>440</v>
       </c>
@@ -17556,7 +17572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>441</v>
       </c>
@@ -17606,7 +17622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>443</v>
       </c>
@@ -17626,7 +17642,7 @@
         <v>44</v>
       </c>
       <c r="G316">
-        <v>76.45999999999999</v>
+        <v>76.459999999999994</v>
       </c>
       <c r="H316">
         <v>159000</v>
@@ -17656,7 +17672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>444</v>
       </c>
@@ -17706,7 +17722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>445</v>
       </c>
@@ -17756,7 +17772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>446</v>
       </c>
@@ -17806,7 +17822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>446</v>
       </c>
@@ -17826,7 +17842,7 @@
         <v>692</v>
       </c>
       <c r="G320">
-        <v>17.9</v>
+        <v>17.899999999999999</v>
       </c>
       <c r="H320">
         <v>37200</v>
@@ -17856,7 +17872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:16">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>446</v>
       </c>
@@ -17906,7 +17922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:16">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>446</v>
       </c>
@@ -17956,7 +17972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:16">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>450</v>
       </c>
@@ -18006,7 +18022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:16">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>450</v>
       </c>
@@ -18056,7 +18072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:16">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>450</v>
       </c>
@@ -18103,7 +18119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:16">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>459</v>
       </c>
@@ -18144,7 +18160,7 @@
         <v>26300</v>
       </c>
       <c r="N326">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O326" t="s">
         <v>498</v>
@@ -18153,7 +18169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:16">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>459</v>
       </c>
@@ -18203,7 +18219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:16">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>459</v>
       </c>
@@ -18253,7 +18269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:16">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>459</v>
       </c>
@@ -18303,7 +18319,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="330" spans="1:16">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>464</v>
       </c>
@@ -18353,7 +18369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:16">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>465</v>
       </c>
@@ -18403,7 +18419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:16">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>467</v>
       </c>
@@ -18453,7 +18469,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:16">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>467</v>
       </c>
@@ -18503,7 +18519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:16">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>467</v>
       </c>
@@ -18553,7 +18569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:16">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>471</v>
       </c>
@@ -18600,7 +18616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="336" spans="1:16">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>471</v>
       </c>
@@ -18650,7 +18666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:16">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>473</v>
       </c>
@@ -18700,7 +18716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:16">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>473</v>
       </c>
@@ -18750,7 +18766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:16">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>473</v>
       </c>
@@ -18800,7 +18816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="340" spans="1:16">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>477</v>
       </c>
@@ -18850,7 +18866,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:16">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>477</v>
       </c>
@@ -18900,7 +18916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:16">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>477</v>
       </c>
@@ -18950,7 +18966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="343" spans="1:16">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>482</v>
       </c>
@@ -19000,7 +19016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:16">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>484</v>
       </c>
@@ -19050,7 +19066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="345" spans="1:16">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>486</v>
       </c>
@@ -19100,7 +19116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="346" spans="1:16">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>487</v>
       </c>
@@ -19150,7 +19166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:16">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>490</v>
       </c>
@@ -19200,7 +19216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:16">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>490</v>
       </c>
@@ -19247,7 +19263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="349" spans="1:16">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>493</v>
       </c>
@@ -19267,7 +19283,7 @@
         <v>654</v>
       </c>
       <c r="G349">
-        <v>19.49</v>
+        <v>19.489999999999998</v>
       </c>
       <c r="H349">
         <v>40500</v>
@@ -19297,7 +19313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:16">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>493</v>
       </c>
@@ -19317,7 +19333,7 @@
         <v>725</v>
       </c>
       <c r="G350">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="H350">
         <v>34700</v>
@@ -19347,7 +19363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:16">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>493</v>
       </c>
@@ -19394,7 +19410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:16">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>496</v>
       </c>
@@ -19444,7 +19460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:16">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>496</v>
       </c>
@@ -19494,7 +19510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:16">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>496</v>
       </c>
@@ -19541,7 +19557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>496</v>
       </c>
@@ -19591,7 +19607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:16">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>496</v>
       </c>
@@ -19641,7 +19657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="357" spans="1:16">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>501</v>
       </c>
@@ -19688,7 +19704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="358" spans="1:16">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>501</v>
       </c>
@@ -19738,7 +19754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:16">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>505</v>
       </c>
@@ -19758,7 +19774,7 @@
         <v>337</v>
       </c>
       <c r="G359">
-        <v>35.45</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="H359">
         <v>73700</v>
@@ -19788,7 +19804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:16">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>505</v>
       </c>
@@ -19838,7 +19854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="1:16">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>507</v>
       </c>
@@ -19858,7 +19874,7 @@
         <v>41</v>
       </c>
       <c r="G361">
-        <v>77.06999999999999</v>
+        <v>77.069999999999993</v>
       </c>
       <c r="H361">
         <v>160300</v>
@@ -19888,7 +19904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="362" spans="1:16">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>507</v>
       </c>
@@ -19938,7 +19954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:16">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>510</v>
       </c>
@@ -19988,7 +20004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:16">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>510</v>
       </c>
@@ -20038,7 +20054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:16">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>513</v>
       </c>
@@ -20088,7 +20104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:16">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>514</v>
       </c>
@@ -20138,7 +20154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:16">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>514</v>
       </c>
@@ -20188,7 +20204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:16">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>517</v>
       </c>
@@ -20238,7 +20254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>517</v>
       </c>
@@ -20288,7 +20304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>517</v>
       </c>
@@ -20338,7 +20354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>520</v>
       </c>
@@ -20385,7 +20401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>522</v>
       </c>
@@ -20435,7 +20451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>523</v>
       </c>
@@ -20485,7 +20501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>523</v>
       </c>
@@ -20535,7 +20551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>523</v>
       </c>
@@ -20585,7 +20601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>528</v>
       </c>
@@ -20632,7 +20648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>528</v>
       </c>
@@ -20682,7 +20698,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>528</v>
       </c>
@@ -20732,7 +20748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>532</v>
       </c>
@@ -20782,7 +20798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>532</v>
       </c>
@@ -20832,7 +20848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>532</v>
       </c>
@@ -20852,7 +20868,7 @@
         <v>259</v>
       </c>
       <c r="G381">
-        <v>38.91</v>
+        <v>38.909999999999997</v>
       </c>
       <c r="H381">
         <v>80900</v>
@@ -20882,7 +20898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>532</v>
       </c>
@@ -20932,7 +20948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>537</v>
       </c>
@@ -20952,7 +20968,7 @@
         <v>359</v>
       </c>
       <c r="G383">
-        <v>33.88</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="H383">
         <v>70500</v>
@@ -20982,7 +20998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>537</v>
       </c>
@@ -21032,7 +21048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>537</v>
       </c>
@@ -21082,7 +21098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>537</v>
       </c>
@@ -21129,7 +21145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>541</v>
       </c>
@@ -21179,7 +21195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>541</v>
       </c>
@@ -21229,7 +21245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>541</v>
       </c>
@@ -21249,7 +21265,7 @@
         <v>377</v>
       </c>
       <c r="G389">
-        <v>32.13</v>
+        <v>32.130000000000003</v>
       </c>
       <c r="H389">
         <v>66800</v>
@@ -21279,7 +21295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>541</v>
       </c>
@@ -21329,7 +21345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>546</v>
       </c>
@@ -21379,7 +21395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>546</v>
       </c>
@@ -21429,7 +21445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>546</v>
       </c>
@@ -21476,7 +21492,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>546</v>
       </c>
@@ -21526,7 +21542,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>550</v>
       </c>
@@ -21573,7 +21589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>550</v>
       </c>
@@ -21623,7 +21639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>554</v>
       </c>
@@ -21673,7 +21689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>557</v>
       </c>
@@ -21723,7 +21739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>557</v>
       </c>
@@ -21773,7 +21789,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>561</v>
       </c>
@@ -21820,7 +21836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>561</v>
       </c>
@@ -21870,7 +21886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>561</v>
       </c>
@@ -21920,7 +21936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>564</v>
       </c>
@@ -21967,7 +21983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>565</v>
       </c>
@@ -22017,7 +22033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>565</v>
       </c>
@@ -22037,7 +22053,7 @@
         <v>268</v>
       </c>
       <c r="G405">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="H405">
         <v>80000</v>
@@ -22067,7 +22083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>565</v>
       </c>
@@ -22117,7 +22133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>569</v>
       </c>
@@ -22167,7 +22183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>569</v>
       </c>
@@ -22217,7 +22233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>573</v>
       </c>
@@ -22267,7 +22283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>573</v>
       </c>
@@ -22317,7 +22333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>573</v>
       </c>
@@ -22367,7 +22383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>573</v>
       </c>
@@ -22417,7 +22433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>578</v>
       </c>
@@ -22467,7 +22483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>580</v>
       </c>
@@ -22487,7 +22503,7 @@
         <v>289</v>
       </c>
       <c r="G414">
-        <v>37.48</v>
+        <v>37.479999999999997</v>
       </c>
       <c r="H414">
         <v>78000</v>
@@ -22517,7 +22533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>583</v>
       </c>
@@ -22564,7 +22580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>583</v>
       </c>
@@ -22584,7 +22600,7 @@
         <v>320</v>
       </c>
       <c r="G416">
-        <v>36.41</v>
+        <v>36.409999999999997</v>
       </c>
       <c r="H416">
         <v>75700</v>
@@ -22614,7 +22630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>587</v>
       </c>
@@ -22661,7 +22677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>587</v>
       </c>
@@ -22711,7 +22727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>591</v>
       </c>
@@ -22731,7 +22747,7 @@
         <v>634</v>
       </c>
       <c r="G419">
-        <v>20.42</v>
+        <v>20.420000000000002</v>
       </c>
       <c r="H419">
         <v>42500</v>
@@ -22761,7 +22777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>591</v>
       </c>
@@ -22811,7 +22827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>591</v>
       </c>
@@ -22861,7 +22877,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>594</v>
       </c>
@@ -22911,7 +22927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>598</v>
       </c>
@@ -22961,7 +22977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>599</v>
       </c>
@@ -23008,7 +23024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>599</v>
       </c>
@@ -23058,7 +23074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>609</v>
       </c>
@@ -23108,7 +23124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>613</v>
       </c>
@@ -23158,7 +23174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>613</v>
       </c>
@@ -23208,7 +23224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>613</v>
       </c>
@@ -23228,7 +23244,7 @@
         <v>350</v>
       </c>
       <c r="G429">
-        <v>34.52</v>
+        <v>34.520000000000003</v>
       </c>
       <c r="H429">
         <v>71800</v>
@@ -23258,7 +23274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>618</v>
       </c>
@@ -23308,7 +23324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>618</v>
       </c>
@@ -23358,7 +23374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>618</v>
       </c>
@@ -23408,7 +23424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:16">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>626</v>
       </c>
@@ -23458,7 +23474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:16">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>626</v>
       </c>
@@ -23508,7 +23524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:16">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>631</v>
       </c>
@@ -23558,7 +23574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="436" spans="1:16">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>632</v>
       </c>
@@ -23608,7 +23624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:16">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>632</v>
       </c>
@@ -23658,7 +23674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:16">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>632</v>
       </c>
@@ -23708,7 +23724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:16">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>632</v>
       </c>
@@ -23728,7 +23744,7 @@
         <v>36</v>
       </c>
       <c r="G439">
-        <v>78.48999999999999</v>
+        <v>78.489999999999995</v>
       </c>
       <c r="H439">
         <v>163300</v>
@@ -23758,7 +23774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:16">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>637</v>
       </c>
@@ -23808,7 +23824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:16">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>637</v>
       </c>
@@ -23858,7 +23874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:16">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>637</v>
       </c>
@@ -23908,7 +23924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:16">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>637</v>
       </c>
@@ -23955,7 +23971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:16">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>644</v>
       </c>
@@ -24005,7 +24021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="445" spans="1:16">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>644</v>
       </c>
@@ -24055,7 +24071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="446" spans="1:16">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>646</v>
       </c>
@@ -24105,7 +24121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="447" spans="1:16">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>654</v>
       </c>
@@ -24155,7 +24171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="448" spans="1:16">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>654</v>
       </c>
@@ -24205,7 +24221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:16">
+    <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>654</v>
       </c>
@@ -24255,7 +24271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:16">
+    <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>654</v>
       </c>
@@ -24305,7 +24321,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:16">
+    <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>658</v>
       </c>
@@ -24346,7 +24362,7 @@
         <v>16200</v>
       </c>
       <c r="N451">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O451" t="s">
         <v>498</v>
@@ -24355,7 +24371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:16">
+    <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>658</v>
       </c>
@@ -24402,7 +24418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:16">
+    <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>658</v>
       </c>
@@ -24422,7 +24438,7 @@
         <v>31</v>
       </c>
       <c r="G453">
-        <v>82.04000000000001</v>
+        <v>82.04</v>
       </c>
       <c r="H453">
         <v>170700</v>
@@ -24452,7 +24468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:16">
+    <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>658</v>
       </c>
@@ -24502,7 +24518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:16">
+    <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>663</v>
       </c>
@@ -24549,7 +24565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="456" spans="1:16">
+    <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>663</v>
       </c>
@@ -24599,7 +24615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="457" spans="1:16">
+    <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>663</v>
       </c>
@@ -24649,7 +24665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="458" spans="1:16">
+    <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>663</v>
       </c>
@@ -24699,7 +24715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:16">
+    <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>671</v>
       </c>
@@ -24749,7 +24765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="460" spans="1:16">
+    <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>671</v>
       </c>
@@ -24799,7 +24815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:16">
+    <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>671</v>
       </c>
@@ -24849,7 +24865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:16">
+    <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>671</v>
       </c>
@@ -24899,7 +24915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:16">
+    <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>678</v>
       </c>
@@ -24949,7 +24965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="1:16">
+    <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>681</v>
       </c>
@@ -24999,7 +25015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" spans="1:16">
+    <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>681</v>
       </c>
@@ -25049,7 +25065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:16">
+    <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>681</v>
       </c>
@@ -25099,7 +25115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:16">
+    <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>681</v>
       </c>
@@ -25149,7 +25165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="468" spans="1:16">
+    <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>681</v>
       </c>
@@ -25199,7 +25215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:16">
+    <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>687</v>
       </c>
@@ -25246,7 +25262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="470" spans="1:16">
+    <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>687</v>
       </c>
@@ -25287,7 +25303,7 @@
         <v>7600</v>
       </c>
       <c r="N470">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="O470" t="s">
         <v>495</v>
@@ -25296,7 +25312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:16">
+    <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>687</v>
       </c>
@@ -25316,7 +25332,7 @@
         <v>367</v>
       </c>
       <c r="G471">
-        <v>33.16</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="H471">
         <v>69000</v>
@@ -25346,7 +25362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:16">
+    <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>687</v>
       </c>
@@ -25396,7 +25412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="1:16">
+    <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>693</v>
       </c>
@@ -25446,7 +25462,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:16">
+    <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>693</v>
       </c>
@@ -25496,7 +25512,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="475" spans="1:16">
+    <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>693</v>
       </c>
@@ -25546,7 +25562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="476" spans="1:16">
+    <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>693</v>
       </c>
@@ -25596,7 +25612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="477" spans="1:16">
+    <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>700</v>
       </c>
@@ -25646,7 +25662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:16">
+    <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>700</v>
       </c>
@@ -25693,7 +25709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="479" spans="1:16">
+    <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>704</v>
       </c>
@@ -25743,7 +25759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:16">
+    <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>704</v>
       </c>
@@ -25793,7 +25809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="481" spans="1:16">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>707</v>
       </c>
